--- a/results/breakdown/hydrogen peroxide production, AO real, fossil hydrogen.xlsx
+++ b/results/breakdown/hydrogen peroxide production, AO real, fossil hydrogen.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="12">
   <si>
     <t>target</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>'market for anthraquinone' (kilogram, GLO, None)</t>
+  </si>
+  <si>
+    <t>'market for benzene' (kilogram, RoW, None)</t>
   </si>
   <si>
     <t>'market for wastewater, average' (cubic meter, RoW, None)</t>
@@ -404,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -423,7 +426,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
@@ -432,7 +435,7 @@
         <v>4</v>
       </c>
       <c r="D2">
-        <v>1.281209674332068</v>
+        <v>1.285683453913668</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -466,7 +469,7 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>0.06711642649726116</v>
+        <v>0.06711642649726114</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -483,7 +486,7 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>0.0002435792672829208</v>
+        <v>0.004473779517525409</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -500,7 +503,7 @@
         <v>8</v>
       </c>
       <c r="D6">
-        <v>0.06008484844983373</v>
+        <v>0.00024357926728292</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -517,7 +520,7 @@
         <v>9</v>
       </c>
       <c r="D7">
-        <v>0.001051107755855214</v>
+        <v>0.06008484844983375</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -534,9 +537,26 @@
         <v>10</v>
       </c>
       <c r="D8">
+        <v>0.001051107755855215</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="1">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9">
         <v>0.1373612714488579</v>
       </c>
-      <c r="E8">
+      <c r="E9">
         <v>1</v>
       </c>
     </row>
